--- a/excel_templates/single_cell_flex_manifest_template.xlsx
+++ b/excel_templates/single_cell_flex_manifest_template.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>PT1899</t>
+          <t>P_5P2QIUH2</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>SM7316-11566</t>
+          <t>S_0000012</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>AL1549608_T_FLEX</t>
+          <t>AL_0000025_T_10xFlexGEX</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>MODEL-PARENT-001</t>
+          <t>CNMC-XD760</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>MODEL-GM-001</t>
+          <t>CNMC-XD760-mCherry-Luciferase</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>GCAT</t>
+          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>flex trial</t>
+          <t>RBT</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">

--- a/excel_templates/single_cell_flex_manifest_template.xlsx
+++ b/excel_templates/single_cell_flex_manifest_template.xlsx
@@ -2540,7 +2540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO1"/>
+  <dimension ref="A1:BP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2610,6 +2610,7 @@
     <col width="24" customWidth="1" min="65" max="65"/>
     <col width="24" customWidth="1" min="66" max="66"/>
     <col width="24" customWidth="1" min="67" max="67"/>
+    <col width="24" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2755,202 +2756,207 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>file_platform</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>sequencing_batch</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>file_size</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>file_hash_value</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>sequencing_center</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>instrument_platform</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
           <t>instrument_model</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>end_bias</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>library_type</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>library_construction</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>feature_type</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>probe_set</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>probe_spike_in</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>probe_spike_in_description</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>total_reads</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_read</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_offset</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_size</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>cell_barcode_read</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>cell_barcode_offset</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>cell_barcode_size</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>cDNA_read</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>cDNA_read_offset</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>flow_cell_barcode</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>lane_number</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>adapter_sequencing</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>target_cell_number</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>reference_genome</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="22">
+  <dataValidations count="21">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
@@ -2966,56 +2972,53 @@
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$20</formula1>
     </dataValidation>
-    <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$F$2:$F$26</formula1>
     </dataValidation>
-    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$G$2:$G$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$9</formula1>
-    </dataValidation>
-    <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$2</formula1>
-    </dataValidation>
     <dataValidation sqref="AM2:AM1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$4</formula1>
+      <formula1>'Lists'!$H$2:$H$2</formula1>
     </dataValidation>
     <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$2</formula1>
+      <formula1>'Lists'!$I$2:$I$4</formula1>
     </dataValidation>
     <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$9</formula1>
+      <formula1>'Lists'!$J$2:$J$2</formula1>
     </dataValidation>
     <dataValidation sqref="AP2:AP1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$M$2:$M$6</formula1>
+      <formula1>'Lists'!$K$2:$K$9</formula1>
     </dataValidation>
-    <dataValidation sqref="AR2:AR1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$N$2:$N$2</formula1>
+    <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$L$2:$L$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$O$2:$O$3</formula1>
+    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$M$2:$M$2</formula1>
     </dataValidation>
-    <dataValidation sqref="AW2:AW1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$N$2:$N$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AX2:AX1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$O$2:$O$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="BA2:BA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$P$2:$P$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AZ2:AZ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BD2:BD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$Q$2:$Q$6</formula1>
     </dataValidation>
-    <dataValidation sqref="BC2:BC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$R$2:$R$6</formula1>
+    <dataValidation sqref="BF2:BF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$R$2:$R$4</formula1>
     </dataValidation>
-    <dataValidation sqref="BE2:BE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BG2:BG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$S$2:$S$4</formula1>
     </dataValidation>
-    <dataValidation sqref="BF2:BF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$T$2:$T$4</formula1>
+    <dataValidation sqref="BJ2:BJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$T$2:$T$3</formula1>
     </dataValidation>
-    <dataValidation sqref="BI2:BI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BN2:BN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$U$2:$U$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="BM2:BM1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$V$2:$V$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3028,7 +3031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3069,75 +3072,70 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>end_bias</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>end_bias</t>
+          <t>library_type</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>library_type</t>
+          <t>library_selection</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>library_selection</t>
+          <t>library_strand</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>library_strand</t>
+          <t>feature_type</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>feature_type</t>
+          <t>probe_spike_in</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>probe_spike_in</t>
+          <t>UMI_barcode_read</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>UMI_barcode_read</t>
+          <t>cell_barcode_read</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>cell_barcode_read</t>
+          <t>cDNA_read</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>cDNA_read</t>
+          <t>is_paired_end</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>is_paired_end</t>
+          <t>read_pair_number</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>read_pair_number</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
-        <is>
-          <t>is_adapter_trimmed</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
@@ -3181,42 +3179,42 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Complete Genomics</t>
+          <t>10x Flex GEX</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10x Flex GEX</t>
+          <t>3'-end</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3'-end</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>Affinity Enrichment</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Affinity Enrichment</t>
+          <t>Stranded</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Stranded</t>
+          <t>gex</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>gex</t>
+          <t>True</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>index1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -3231,25 +3229,20 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>index1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3286,62 +3279,57 @@
           <t>SHA1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Illumina</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>5'-end</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Hybrid Selection</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Hybrid Selection</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>Unstranded</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>index2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>index2</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>index2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>index2</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>index2</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>index2</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3373,26 +3361,26 @@
           <t>SHA256</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Ion Torrent</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Full-length</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>miRNA Size Fractionation</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>miRNA Size Fractionation</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
           <t>First Stranded</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>read1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>read1</t>
@@ -3405,15 +3393,10 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>read1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3445,32 +3428,27 @@
           <t>SHA512</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>LS454</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PCR</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PCR</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
           <t>Second Stranded</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>read2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
-        <is>
-          <t>read2</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
@@ -3502,32 +3480,27 @@
           <t>ETag</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SOLiD</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Poly-T Enrichment</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Poly-T Enrichment</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
           <t>Not Applicable</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
@@ -3549,12 +3522,7 @@
           <t>GVCF</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ONT</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Random</t>
         </is>
@@ -3576,12 +3544,7 @@
           <t>VCF</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>DNBSEQ</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>rRNA Depletion</t>
         </is>
@@ -3603,12 +3566,7 @@
           <t>TBI</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>

--- a/excel_templates/single_cell_flex_manifest_template.xlsx
+++ b/excel_templates/single_cell_flex_manifest_template.xlsx
@@ -2756,7 +2756,7 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>file_platform</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">

--- a/excel_templates/single_cell_flex_manifest_template.xlsx
+++ b/excel_templates/single_cell_flex_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SMB directory path on the L Drive for the source data</t>
+          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>S3 URI for the submitted data location</t>
+          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -1324,20 +1324,24 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>sequencing_batch</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Sequencing batch identifier</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Source platform where files are stored and from which they are harmonized</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1345,7 +1349,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30-XXXXXXXX</t>
+          <t>bti_aws</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1353,17 +1357,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>sequencing_batch</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Name of the file. In pooled Flex data, the same file may appear once per Cell Ranger sample assignment</t>
+          <t>Sequencing batch identifier</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -1374,7 +1378,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>FLEX_POOL_01_S1_L001_R1_001.fastq.gz</t>
+          <t>30-XXXXXXXX</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1382,7 +1386,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>file_format</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1392,14 +1396,10 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Format of the file</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
-        </is>
-      </c>
+          <t>Name of the file. In pooled Flex data, the same file may appear once per Cell Ranger sample assignment</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>FASTQ</t>
+          <t>FLEX_POOL_01_S1_L001_R1_001.fastq.gz</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1415,7 +1415,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>file_size</t>
+          <t>file_format</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1425,18 +1425,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Reported file size in bytes</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr"/>
+          <t>Format of the file</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>529600</t>
+          <t>FASTQ</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1444,7 +1448,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>file_hash_type</t>
+          <t>file_size</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1454,22 +1458,18 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Hash algorithm used to generate file hash</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
-        </is>
-      </c>
+          <t>Reported file size in bytes</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>MD5</t>
+          <t>529600</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1477,7 +1477,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>file_hash_value</t>
+          <t>file_hash_type</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1487,10 +1487,14 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Full hash value of the file</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
+          <t>Hash algorithm used to generate file hash</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
+          <t>MD5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1506,17 +1510,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>sequencing_center</t>
+          <t>file_hash_value</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Name of the center generating sequencing data</t>
+          <t>Full hash value of the file</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -1527,7 +1531,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Harvard Med School</t>
+          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1535,24 +1539,20 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>sequencing_center</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Name of the platform used to obtain data</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
-        </is>
-      </c>
+          <t>Name of the center generating sequencing data</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>Harvard Med School</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1568,20 +1568,24 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>instrument_model</t>
+          <t>instrument_platform</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Specific model of sequencing instrument used</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>Name of the platform used to obtain data</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1589,7 +1593,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>NovaSeq 6000</t>
+          <t>Illumina</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1597,24 +1601,20 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>instrument_model</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>The sequencing strategy used to generate the data file</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>"10x Flex GEX"</t>
-        </is>
-      </c>
+          <t>Specific model of sequencing instrument used</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>10x Flex GEX</t>
+          <t>NovaSeq 6000</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1630,7 +1630,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>end_bias</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>The end of the cDNA molecule that is preferentially sequenced</t>
+          <t>The sequencing strategy used to generate the data file</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>"3'-end", "5'-end", "Full-length"</t>
+          <t>"10x Flex GEX"</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3'-end</t>
+          <t>10x Flex GEX</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>library_type</t>
+          <t>end_bias</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Library modality</t>
+          <t>The end of the cDNA molecule that is preferentially sequenced</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>"GEX"</t>
+          <t>"3'-end", "5'-end", "Full-length"</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>3'-end</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>library_selection</t>
+          <t>library_type</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Library selection method</t>
+          <t>Library modality</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random", "rRNA Depletion", "Other"</t>
+          <t>"GEX"</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Hybrid Selection</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1729,7 +1729,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>library_strand</t>
+          <t>library_selection</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Library strandedness</t>
+          <t>Library selection method</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Not Applicable"</t>
+          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random", "rRNA Depletion", "Other"</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Hybrid Selection</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>library_construction</t>
+          <t>library_strand</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1772,10 +1772,14 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Library construction method including version</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>Library strandedness</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1783,7 +1787,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>10x Flex</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1791,7 +1795,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>feature_type</t>
+          <t>library_construction</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1801,14 +1805,10 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>10x feature type represented by the library</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>"gex"</t>
-        </is>
-      </c>
+          <t>Library construction method including version</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>gex</t>
+          <t>10x Flex</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -1824,7 +1824,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>probe_set</t>
+          <t>feature_type</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1834,10 +1834,14 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>10x Flex transcriptome probe set name and version used for alignment/counting. Use a stable probe set name/version rather than a local machine-specific path</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>10x feature type represented by the library</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>"gex"</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1845,7 +1849,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Chromium_Mouse_Transcriptome_Probe_Set_v2.0.0_GRCm39-2024-A</t>
+          <t>gex</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -1853,7 +1857,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>probe_spike_in</t>
+          <t>probe_set</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1863,22 +1867,18 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Were custom probes spiked into the standard 10x Flex probe set?</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>10x Flex transcriptome probe set name and version used for alignment/counting. Use a stable probe set name/version rather than a local machine-specific path</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Chromium_Mouse_Transcriptome_Probe_Set_v2.0.0_GRCm39-2024-A</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -1886,28 +1886,32 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>probe_spike_in_description</t>
+          <t>probe_spike_in</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Were custom probes spiked into the standard 10x Flex probe set?</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>False</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Description of custom spike-in probes when `probe_spike_in` is True. Use NA when no custom probes were spiked in</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>CD123/B7H3 CAR construct spike-in probes</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -1915,7 +1919,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>total_reads</t>
+          <t>probe_spike_in_description</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1925,18 +1929,18 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Total number of reads that align to the reference</t>
+          <t>Description of custom spike-in probes when `probe_spike_in` is True. Use NA when no custom probes were spiked in</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>525600</t>
+          <t>CD123/B7H3 CAR construct spike-in probes</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -1944,32 +1948,28 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_read</t>
+          <t>total_reads</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the UMI barcode</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>Total number of reads that align to the reference</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>read1</t>
+          <t>525600</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -1977,7 +1977,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_offset</t>
+          <t>UMI_barcode_read</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1987,18 +1987,22 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Offset in sequence of the UMI barcode</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr"/>
+          <t>The type of read that contains the UMI barcode</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>read1</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2006,7 +2010,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_size</t>
+          <t>UMI_barcode_offset</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2016,7 +2020,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Length of the UMI barcode sequence</t>
+          <t>Offset in sequence of the UMI barcode</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2035,7 +2039,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>cell_barcode_read</t>
+          <t>UMI_barcode_size</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2045,22 +2049,18 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the cell barcode</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>Length of the UMI barcode sequence</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>read1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2068,7 +2068,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>cell_barcode_offset</t>
+          <t>cell_barcode_read</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2078,18 +2078,22 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Offset in sequence of the cell barcode</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr"/>
+          <t>The type of read that contains the cell barcode</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>read1</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2097,7 +2101,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>cell_barcode_size</t>
+          <t>cell_barcode_offset</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2107,7 +2111,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Length of the cell barcode sequence</t>
+          <t>Offset in sequence of the cell barcode</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -2118,7 +2122,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -2126,7 +2130,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>cDNA_read</t>
+          <t>cell_barcode_size</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2136,22 +2140,18 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the cDNA read</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>Length of the cell barcode sequence</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>read2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2159,7 +2159,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>cDNA_read_offset</t>
+          <t>cDNA_read</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2169,18 +2169,22 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Offset in sequence of the cDNA read</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>The type of read that contains the cDNA read</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>read2</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2188,7 +2192,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>is_paired_end</t>
+          <t>cDNA_read_offset</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2198,22 +2202,18 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>If FASTQ/BAM files, are the reads paired end?</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False", "NA"</t>
-        </is>
-      </c>
+          <t>Offset in sequence of the cDNA read</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>boolean/string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2221,32 +2221,32 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>read_pair_number</t>
+          <t>is_paired_end</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files</t>
+          <t>If FASTQ/BAM files, are the reads paired end?</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>"R1", "R2", "NA"</t>
+          <t>"True", "False", "NA"</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean/string</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>flow_cell_barcode</t>
+          <t>read_pair_number</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2264,10 +2264,14 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Flow cell barcode. Required when inputs are FASTQ files</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>"R1", "R2", "NA"</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -2275,7 +2279,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>H0164ALXX</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2283,7 +2287,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>lane_number</t>
+          <t>flow_cell_barcode</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2293,7 +2297,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Physical sequencing lane number. Required when inputs are FASTQ files</t>
+          <t>Flow cell barcode. Required when inputs are FASTQ files</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2304,7 +2308,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>H0164ALXX</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2312,7 +2316,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>is_adapter_trimmed</t>
+          <t>lane_number</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2322,22 +2326,18 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Were adapters trimmed from sequencing data? Required when inputs are FASTQ files</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>Physical sequencing lane number. Required when inputs are FASTQ files</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>adapter_sequencing</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2355,18 +2355,22 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Base sequence of the sequencing adapter. Required when adapters were not trimmed</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr"/>
+          <t>Were adapters trimmed from sequencing data? Required when inputs are FASTQ files</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -2374,7 +2378,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>target_cell_number</t>
+          <t>adapter_sequencing</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2384,18 +2388,18 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Target number of cells to recover for the assay</t>
+          <t>Base sequence of the sequencing adapter. Required when adapters were not trimmed</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2403,28 +2407,28 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>reference_genome</t>
+          <t>target_cell_number</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version</t>
+          <t>Target number of cells to recover for the assay</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>GRCh38</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -2432,7 +2436,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>reference_genome</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2442,22 +2446,18 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Is the sample preserved in FFPE?</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>Reference genome version</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>GRCh38</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -2465,7 +2465,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2475,30 +2475,30 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
+          <t>Is the sample preserved in FFPE?</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2519,17 +2519,50 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>RBT</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G68"/>
+  <autoFilter ref="A1:G69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2956,7 +2989,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="21">
+  <dataValidations count="23">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
@@ -2972,53 +3005,59 @@
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$20</formula1>
     </dataValidation>
+    <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$F$2:$F$8</formula1>
+    </dataValidation>
     <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$F$2:$F$26</formula1>
+      <formula1>'Lists'!$G$2:$G$26</formula1>
     </dataValidation>
     <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$G$2:$G$6</formula1>
+      <formula1>'Lists'!$H$2:$H$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$I$2:$I$9</formula1>
     </dataValidation>
     <dataValidation sqref="AM2:AM1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$2</formula1>
+      <formula1>'Lists'!$J$2:$J$2</formula1>
     </dataValidation>
     <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$4</formula1>
+      <formula1>'Lists'!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$2</formula1>
+      <formula1>'Lists'!$L$2:$L$2</formula1>
     </dataValidation>
     <dataValidation sqref="AP2:AP1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$9</formula1>
+      <formula1>'Lists'!$M$2:$M$9</formula1>
     </dataValidation>
     <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$6</formula1>
+      <formula1>'Lists'!$N$2:$N$6</formula1>
     </dataValidation>
     <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$M$2:$M$2</formula1>
+      <formula1>'Lists'!$O$2:$O$2</formula1>
     </dataValidation>
     <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$N$2:$N$3</formula1>
+      <formula1>'Lists'!$P$2:$P$3</formula1>
     </dataValidation>
     <dataValidation sqref="AX2:AX1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$O$2:$O$6</formula1>
+      <formula1>'Lists'!$Q$2:$Q$6</formula1>
     </dataValidation>
     <dataValidation sqref="BA2:BA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$P$2:$P$6</formula1>
+      <formula1>'Lists'!$R$2:$R$6</formula1>
     </dataValidation>
     <dataValidation sqref="BD2:BD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$Q$2:$Q$6</formula1>
+      <formula1>'Lists'!$S$2:$S$6</formula1>
     </dataValidation>
     <dataValidation sqref="BF2:BF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$R$2:$R$4</formula1>
+      <formula1>'Lists'!$T$2:$T$4</formula1>
     </dataValidation>
     <dataValidation sqref="BG2:BG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$S$2:$S$4</formula1>
+      <formula1>'Lists'!$U$2:$U$4</formula1>
     </dataValidation>
     <dataValidation sqref="BJ2:BJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$T$2:$T$3</formula1>
+      <formula1>'Lists'!$V$2:$V$3</formula1>
     </dataValidation>
     <dataValidation sqref="BN2:BN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$U$2:$U$3</formula1>
+      <formula1>'Lists'!$W$2:$W$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3031,7 +3070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3062,80 +3101,90 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>file_source_platform</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>instrument_platform</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>end_bias</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>library_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>feature_type</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>probe_spike_in</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>UMI_barcode_read</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>cell_barcode_read</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>cDNA_read</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
@@ -3169,80 +3218,90 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>bti_aws</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>FASTQ</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>MD5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Complete Genomics</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>10x Flex GEX</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>3'-end</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>GEX</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Affinity Enrichment</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Stranded</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>gex</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3271,65 +3330,75 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>local_drive</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>BAM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>SHA1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Illumina</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>5'-end</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Hybrid Selection</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Unstranded</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3353,50 +3422,60 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>bti_aws_and_local_drive</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>BAI</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>SHA256</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Ion Torrent</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Full-length</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>miRNA Size Fractionation</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>First Stranded</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3420,35 +3499,45 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>cgc</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>CRAM</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>SHA512</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LS454</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>PCR</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Second Stranded</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
@@ -3472,35 +3561,45 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>kids_first</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>CRAI</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>ETag</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SOLiD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Poly-T Enrichment</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
@@ -3519,10 +3618,20 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>sra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>GVCF</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ONT</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Random</t>
         </is>
@@ -3541,10 +3650,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>synapse</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>VCF</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>DNBSEQ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>rRNA Depletion</t>
         </is>
@@ -3561,12 +3680,17 @@
           <t>Patient Derived Organoid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>TBI</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -3583,7 +3707,7 @@
           <t>Peripheral Blood Mononuclear Cells</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>MAF</t>
         </is>
@@ -3600,7 +3724,7 @@
           <t>Peripheral Whole Blood</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -3617,7 +3741,7 @@
           <t>Saliva</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
@@ -3634,7 +3758,7 @@
           <t>Solid Tissue</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>DCM</t>
         </is>
@@ -3651,7 +3775,7 @@
           <t>Umbilical Cord Blood</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>IDAT</t>
         </is>
@@ -3663,7 +3787,7 @@
           <t>Patient-Derived T Cells</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>SVS</t>
         </is>
@@ -3675,7 +3799,7 @@
           <t>Modified T Cells</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>GPR</t>
         </is>
@@ -3687,7 +3811,7 @@
           <t>Patient-Derived Primary Cells</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>CNS</t>
         </is>
@@ -3699,7 +3823,7 @@
           <t>iPSC-Derived Organoid</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>TXT</t>
         </is>
@@ -3711,7 +3835,7 @@
           <t>Cerebrospinal Fluid</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
@@ -3723,49 +3847,49 @@
           <t>Embryonic Stem Cell Derived Cell Line</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>PED</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>SEG</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>TAR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>TSV</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>mzML</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>raw</t>
         </is>

--- a/excel_templates/single_cell_flex_manifest_template.xlsx
+++ b/excel_templates/single_cell_flex_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -761,7 +761,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>cell_entity</t>
+          <t>reported_gender</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -771,10 +771,14 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The type of single cell entity</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
+          <t>Reported gender of the participant. Required when organism is "Homo sapiens"</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>"Female", "Male", "Not Reported"</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -782,7 +786,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Whole Cell</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -790,24 +794,20 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>sample_type</t>
+          <t>cell_entity</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Description of the kind of tissue collected with respect to disease status</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>"Tumor", "Normal", "Virus-infected", "Unknown", "Not Reported"</t>
-        </is>
-      </c>
+          <t>The type of single cell entity</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -815,7 +815,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Tumor</t>
+          <t>Whole Cell</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -823,7 +823,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>tumor_descriptor</t>
+          <t>sample_type</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Descriptor of tumor status or clinical tumor context for the sample; must be NA for normal samples</t>
+          <t>Description of the kind of tissue collected with respect to disease status</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>"Deceased", "Initial CNS Tumor", "Metastatic", "Post-treatment", "Primary Tumor", "Progressive", "Progressive Disease Post-Mortem", "Recurrence", "Relapse", "Residual", "Second Malignancy", "Unknown", "NA"</t>
+          <t>"Tumor", "Normal", "Virus-infected", "Unknown", "Not Reported"</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Primary Tumor</t>
+          <t>Tumor</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -856,7 +856,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>composition</t>
+          <t>tumor_descriptor</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Tissue type the collected sample comes from</t>
+          <t>Descriptor of tumor status or clinical tumor context for the sample; must be NA for normal samples</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
+          <t>"Deceased", "Initial CNS Tumor", "Metastatic", "Post-treatment", "Primary Tumor", "Progressive", "Progressive Disease Post-Mortem", "Recurrence", "Relapse", "Residual", "Second Malignancy", "Unknown", "NA"</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Solid Tissue</t>
+          <t>Primary Tumor</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -889,20 +889,24 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>bio_replicate</t>
+          <t>composition</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Label identifying the biological replicate this sample represents</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
+          <t>Tissue type the collected sample comes from</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -910,7 +914,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Rep1</t>
+          <t>Solid Tissue</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -918,7 +922,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>dose_1</t>
+          <t>bio_replicate</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -928,7 +932,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Dose for treatment_1 in a simultaneous combination treatment</t>
+          <t>Label identifying the biological replicate this sample represents</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -939,7 +943,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10 nM</t>
+          <t>Rep1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -947,7 +951,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>dose_2</t>
+          <t>dose_1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -957,7 +961,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Dose for treatment_2 in a simultaneous combination treatment</t>
+          <t>Dose for treatment_1 in a simultaneous combination treatment</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
@@ -968,7 +972,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20 nM</t>
+          <t>10 nM</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -976,7 +980,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>treatment_1</t>
+          <t>dose_2</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -986,7 +990,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>First component of a simultaneous combination treatment administered or applied to the sample</t>
+          <t>Dose for treatment_2 in a simultaneous combination treatment</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -997,7 +1001,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>temozolomide</t>
+          <t>20 nM</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1005,7 +1009,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>treatment_2</t>
+          <t>treatment_1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1015,7 +1019,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Second component of a simultaneous combination treatment administered or applied to the sample</t>
+          <t>First component of a simultaneous combination treatment administered or applied to the sample</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -1026,7 +1030,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>temozolomide</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1034,7 +1038,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>cell_line_composition</t>
+          <t>treatment_2</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1044,7 +1048,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Culture media used for the cell line, for a Derived Cell Line composition</t>
+          <t>Second component of a simultaneous combination treatment administered or applied to the sample</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1055,7 +1059,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>DMEM/F12</t>
+          <t>radiation</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1063,7 +1067,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>cell_line_passage</t>
+          <t>cell_line_composition</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1073,18 +1077,18 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Numeric passage number for the cell line, for a Derived Cell Line composition</t>
+          <t>Culture media used for the cell line, for a Derived Cell Line composition</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>DMEM/F12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1092,7 +1096,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>timepoint</t>
+          <t>cell_line_passage</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1102,18 +1106,18 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Timepoint associated with the treatment, collection, or experiment</t>
+          <t>Numeric passage number for the cell line, for a Derived Cell Line composition</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24h</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1121,7 +1125,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>parental_model_id</t>
+          <t>timepoint</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1131,7 +1135,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Identifier for the parental model. Required for model-derived samples</t>
+          <t>Timepoint associated with the treatment, collection, or experiment</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1142,7 +1146,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>CNMC-XD760</t>
+          <t>24h</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1150,7 +1154,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>model_id</t>
+          <t>parental_model_id</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1160,7 +1164,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Identifier for the submitted model, including genetically modified cell lines or other model derivatives</t>
+          <t>Identifier for the parental model. Required for model-derived samples</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>CNMC-XD760-mCherry-Luciferase</t>
+          <t>CNMC-XD760</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1179,17 +1183,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>cellranger_sample_id</t>
+          <t>model_id</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Cell Ranger multi `sample_id` for this biological sample in the Flex pool</t>
+          <t>Identifier for the submitted model, including genetically modified cell lines or other model derivatives</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -1200,7 +1204,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>FLEX_SAMPLE_001</t>
+          <t>CNMC-XD760-mCherry-Luciferase</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1208,7 +1212,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>probe_barcode_id</t>
+          <t>cellranger_sample_id</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1218,7 +1222,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>One 10x probe barcode assigned to this biological sample in the Cell Ranger multi samples section. If Cell Ranger lists multiple probe barcodes for one sample, represent each sample/probe barcode assignment as separate manifest rows rather than storing a delimited list</t>
+          <t>Cell Ranger multi `sample_id` for this biological sample in the Flex pool</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -1229,7 +1233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>BC001</t>
+          <t>FLEX_SAMPLE_001</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1237,7 +1241,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>library_pool_id</t>
+          <t>probe_barcode_id</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1247,7 +1251,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Identifier for the pooled 10x Flex library or FASTQ pool shared by one or more Cell Ranger samples</t>
+          <t>One 10x probe barcode assigned to this biological sample in the Cell Ranger multi samples section. If Cell Ranger lists multiple probe barcodes for one sample, represent each sample/probe barcode assignment as separate manifest rows rather than storing a delimited list</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -1258,7 +1262,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>FLEX_POOL_01</t>
+          <t>BC001</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1266,17 +1270,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>local_dir_path</t>
+          <t>library_pool_id</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
+          <t>Identifier for the pooled 10x Flex library or FASTQ pool shared by one or more Cell Ranger samples</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -1287,7 +1291,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>smb://cnmc.org/cri/Lab/CancerImmunology-BTI</t>
+          <t>FLEX_POOL_01</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1295,7 +1299,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>aws_s3_path</t>
+          <t>local_dir_path</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1305,7 +1309,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
+          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -1316,7 +1320,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>s3://bucket/prefix</t>
+          <t>smb://cnmc.org/cri/Lab/CancerImmunology-BTI</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1324,24 +1328,20 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>file_source_platform</t>
+          <t>aws_s3_path</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Source platform where files are stored and from which they are harmonized</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
-        </is>
-      </c>
+          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>bti_aws</t>
+          <t>s3://bucket/prefix</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1357,20 +1357,24 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>sequencing_batch</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Sequencing batch identifier</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>Source platform where files are stored and from which they are harmonized</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1378,7 +1382,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30-XXXXXXXX</t>
+          <t>bti_aws</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1386,17 +1390,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>sequencing_batch</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Name of the file. In pooled Flex data, the same file may appear once per Cell Ranger sample assignment</t>
+          <t>Sequencing batch identifier</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -1407,7 +1411,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>FLEX_POOL_01_S1_L001_R1_001.fastq.gz</t>
+          <t>30-XXXXXXXX</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1415,7 +1419,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>file_format</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1425,14 +1429,10 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Format of the file</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
-        </is>
-      </c>
+          <t>Name of the file. In pooled Flex data, the same file may appear once per Cell Ranger sample assignment</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>FASTQ</t>
+          <t>FLEX_POOL_01_S1_L001_R1_001.fastq.gz</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1448,7 +1448,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>file_size</t>
+          <t>file_format</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1458,18 +1458,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Reported file size in bytes</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
+          <t>Format of the file</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>529600</t>
+          <t>FASTQ</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1477,7 +1481,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>file_hash_type</t>
+          <t>file_size</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1487,22 +1491,18 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Hash algorithm used to generate file hash</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
-        </is>
-      </c>
+          <t>Reported file size in bytes</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>MD5</t>
+          <t>529600</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1510,7 +1510,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>file_hash_value</t>
+          <t>file_hash_type</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1520,10 +1520,14 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Full hash value of the file</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>Hash algorithm used to generate file hash</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1531,7 +1535,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
+          <t>MD5</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1539,17 +1543,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>sequencing_center</t>
+          <t>file_hash_value</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Name of the center generating sequencing data</t>
+          <t>Full hash value of the file</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -1560,7 +1564,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Harvard Med School</t>
+          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1568,24 +1572,20 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>instrument_platform</t>
+          <t>sequencing_center</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Name of the platform used to obtain data</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
-        </is>
-      </c>
+          <t>Name of the center generating sequencing data</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>Harvard Med School</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1601,20 +1601,24 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>instrument_model</t>
+          <t>instrument_platform</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Specific model of sequencing instrument used</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
+          <t>Name of the platform used to obtain data</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1622,7 +1626,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>NovaSeq 6000</t>
+          <t>Illumina</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1630,24 +1634,20 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>instrument_model</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>The sequencing strategy used to generate the data file</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>"10x Flex GEX"</t>
-        </is>
-      </c>
+          <t>Specific model of sequencing instrument used</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10x Flex GEX</t>
+          <t>NovaSeq 6000</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>end_bias</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>The end of the cDNA molecule that is preferentially sequenced</t>
+          <t>The sequencing strategy used to generate the data file</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>"3'-end", "5'-end", "Full-length"</t>
+          <t>"10x Flex GEX"</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3'-end</t>
+          <t>10x Flex GEX</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>library_type</t>
+          <t>end_bias</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Library modality</t>
+          <t>The end of the cDNA molecule that is preferentially sequenced</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>"GEX"</t>
+          <t>"3'-end", "5'-end", "Full-length"</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>3'-end</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1729,7 +1729,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>library_selection</t>
+          <t>library_type</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Library selection method</t>
+          <t>Library modality</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random", "rRNA Depletion", "Other"</t>
+          <t>"GEX"</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Hybrid Selection</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>library_strand</t>
+          <t>library_selection</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Library strandedness</t>
+          <t>Library selection method</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Not Applicable"</t>
+          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random", "rRNA Depletion", "Other"</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Hybrid Selection</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1795,7 +1795,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>library_construction</t>
+          <t>library_strand</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1805,10 +1805,14 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Library construction method including version</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
+          <t>Library strandedness</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1816,7 +1820,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>10x Flex</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -1824,7 +1828,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>feature_type</t>
+          <t>library_construction</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1834,14 +1838,10 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>10x feature type represented by the library</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>"gex"</t>
-        </is>
-      </c>
+          <t>Library construction method including version</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>gex</t>
+          <t>10x Flex</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>probe_set</t>
+          <t>feature_type</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1867,10 +1867,14 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>10x Flex transcriptome probe set name and version used for alignment/counting. Use a stable probe set name/version rather than a local machine-specific path</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
+          <t>10x feature type represented by the library</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>"gex"</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1878,7 +1882,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Chromium_Mouse_Transcriptome_Probe_Set_v2.0.0_GRCm39-2024-A</t>
+          <t>gex</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -1886,7 +1890,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>probe_spike_in</t>
+          <t>probe_set</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1896,22 +1900,18 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Were custom probes spiked into the standard 10x Flex probe set?</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>10x Flex transcriptome probe set name and version used for alignment/counting. Use a stable probe set name/version rather than a local machine-specific path</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Chromium_Mouse_Transcriptome_Probe_Set_v2.0.0_GRCm39-2024-A</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -1919,28 +1919,32 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>probe_spike_in_description</t>
+          <t>probe_spike_in</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Were custom probes spiked into the standard 10x Flex probe set?</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>False</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Description of custom spike-in probes when `probe_spike_in` is True. Use NA when no custom probes were spiked in</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>CD123/B7H3 CAR construct spike-in probes</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -1948,7 +1952,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>total_reads</t>
+          <t>probe_spike_in_description</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1958,18 +1962,18 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Total number of reads that align to the reference</t>
+          <t>Description of custom spike-in probes when `probe_spike_in` is True. Use NA when no custom probes were spiked in</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>525600</t>
+          <t>CD123/B7H3 CAR construct spike-in probes</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -1977,32 +1981,28 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_read</t>
+          <t>total_reads</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the UMI barcode</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>Total number of reads that align to the reference</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>read1</t>
+          <t>525600</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2010,7 +2010,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_offset</t>
+          <t>UMI_barcode_read</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2020,18 +2020,22 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Offset in sequence of the UMI barcode</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
+          <t>The type of read that contains the UMI barcode</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>read1</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -2039,7 +2043,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_size</t>
+          <t>UMI_barcode_offset</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2049,7 +2053,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Length of the UMI barcode sequence</t>
+          <t>Offset in sequence of the UMI barcode</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -2068,7 +2072,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>cell_barcode_read</t>
+          <t>UMI_barcode_size</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2078,22 +2082,18 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the cell barcode</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>Length of the UMI barcode sequence</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>read1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2101,7 +2101,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>cell_barcode_offset</t>
+          <t>cell_barcode_read</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2111,18 +2111,22 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Offset in sequence of the cell barcode</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
+          <t>The type of read that contains the cell barcode</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>read1</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -2130,7 +2134,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>cell_barcode_size</t>
+          <t>cell_barcode_offset</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2140,7 +2144,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Length of the cell barcode sequence</t>
+          <t>Offset in sequence of the cell barcode</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2151,7 +2155,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2159,7 +2163,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>cDNA_read</t>
+          <t>cell_barcode_size</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2169,22 +2173,18 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the cDNA read</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>Length of the cell barcode sequence</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>read2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>cDNA_read_offset</t>
+          <t>cDNA_read</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2202,18 +2202,22 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Offset in sequence of the cDNA read</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
+          <t>The type of read that contains the cDNA read</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>read2</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2221,7 +2225,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>is_paired_end</t>
+          <t>cDNA_read_offset</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2231,22 +2235,18 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>If FASTQ/BAM files, are the reads paired end?</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False", "NA"</t>
-        </is>
-      </c>
+          <t>Offset in sequence of the cDNA read</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>boolean/string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2254,32 +2254,32 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>read_pair_number</t>
+          <t>is_paired_end</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files</t>
+          <t>If FASTQ/BAM files, are the reads paired end?</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>"R1", "R2", "NA"</t>
+          <t>"True", "False", "NA"</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean/string</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2287,7 +2287,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>flow_cell_barcode</t>
+          <t>read_pair_number</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2297,10 +2297,14 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Flow cell barcode. Required when inputs are FASTQ files</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr"/>
+          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>"R1", "R2", "NA"</t>
+        </is>
+      </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -2308,7 +2312,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>H0164ALXX</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2316,7 +2320,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>lane_number</t>
+          <t>flow_cell_barcode</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2326,7 +2330,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Physical sequencing lane number. Required when inputs are FASTQ files</t>
+          <t>Flow cell barcode. Required when inputs are FASTQ files</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -2337,7 +2341,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>H0164ALXX</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2345,7 +2349,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>is_adapter_trimmed</t>
+          <t>lane_number</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2355,22 +2359,18 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Were adapters trimmed from sequencing data? Required when inputs are FASTQ files</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>Physical sequencing lane number. Required when inputs are FASTQ files</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -2378,7 +2378,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>adapter_sequencing</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2388,18 +2388,22 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Base sequence of the sequencing adapter. Required when adapters were not trimmed</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
+          <t>Were adapters trimmed from sequencing data? Required when inputs are FASTQ files</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2407,7 +2411,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>target_cell_number</t>
+          <t>adapter_sequencing</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -2417,18 +2421,18 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Target number of cells to recover for the assay</t>
+          <t>Base sequence of the sequencing adapter. Required when adapters were not trimmed</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -2436,28 +2440,28 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>reference_genome</t>
+          <t>target_cell_number</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version</t>
+          <t>Target number of cells to recover for the assay</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>GRCh38</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -2465,7 +2469,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>reference_genome</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2475,22 +2479,18 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Is the sample preserved in FFPE?</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>Reference genome version</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>GRCh38</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -2498,7 +2498,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2508,30 +2508,30 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
+          <t>Is the sample preserved in FFPE?</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -2552,17 +2552,50 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>RBT</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G69"/>
+  <autoFilter ref="A1:G70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2573,7 +2606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BQ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2644,6 +2677,7 @@
     <col width="24" customWidth="1" min="66" max="66"/>
     <col width="24" customWidth="1" min="67" max="67"/>
     <col width="24" customWidth="1" min="68" max="68"/>
+    <col width="24" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2694,370 +2728,378 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>cell_entity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>sample_type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tumor_descriptor</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>composition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>bio_replicate</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dose_1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dose_2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>treatment_1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>treatment_2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>cell_line_composition</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>cell_line_passage</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>timepoint</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>parental_model_id</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>model_id</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>cellranger_sample_id</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>probe_barcode_id</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>library_pool_id</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>local_dir_path</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>aws_s3_path</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>file_source_platform</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>sequencing_batch</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>file_size</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>file_hash_value</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>sequencing_center</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>instrument_platform</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>instrument_model</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>end_bias</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>library_type</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>library_construction</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>feature_type</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>probe_set</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>probe_spike_in</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>probe_spike_in_description</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>total_reads</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_read</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_offset</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_size</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>cell_barcode_read</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>cell_barcode_offset</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>cell_barcode_size</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>cDNA_read</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>cDNA_read_offset</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>flow_cell_barcode</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>lane_number</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>adapter_sequencing</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>target_cell_number</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>reference_genome</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="23">
+  <dataValidations count="24">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$B$2:$B$2</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$6</formula1>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$C$2:$C$4</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$D$2:$D$14</formula1>
+      <formula1>'Lists'!$D$2:$D$6</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$E$2:$E$20</formula1>
+      <formula1>'Lists'!$E$2:$E$14</formula1>
     </dataValidation>
-    <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$F$2:$F$8</formula1>
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$F$2:$F$20</formula1>
     </dataValidation>
-    <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$G$2:$G$26</formula1>
+    <dataValidation sqref="AD2:AD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$G$2:$G$8</formula1>
     </dataValidation>
-    <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$6</formula1>
+    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$H$2:$H$26</formula1>
     </dataValidation>
-    <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$9</formula1>
+    <dataValidation sqref="AI2:AI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$I$2:$I$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AM2:AM1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$2</formula1>
+    <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$J$2:$J$9</formula1>
     </dataValidation>
     <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$4</formula1>
+      <formula1>'Lists'!$K$2:$K$2</formula1>
     </dataValidation>
     <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$2</formula1>
+      <formula1>'Lists'!$L$2:$L$4</formula1>
     </dataValidation>
     <dataValidation sqref="AP2:AP1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$M$2:$M$9</formula1>
+      <formula1>'Lists'!$M$2:$M$2</formula1>
     </dataValidation>
     <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$N$2:$N$6</formula1>
+      <formula1>'Lists'!$N$2:$N$9</formula1>
     </dataValidation>
-    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$O$2:$O$2</formula1>
+    <dataValidation sqref="AR2:AR1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$O$2:$O$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$P$2:$P$3</formula1>
+    <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$P$2:$P$2</formula1>
     </dataValidation>
-    <dataValidation sqref="AX2:AX1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$Q$2:$Q$6</formula1>
+    <dataValidation sqref="AV2:AV1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$Q$2:$Q$3</formula1>
     </dataValidation>
-    <dataValidation sqref="BA2:BA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AY2:AY1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$R$2:$R$6</formula1>
     </dataValidation>
-    <dataValidation sqref="BD2:BD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BB2:BB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$S$2:$S$6</formula1>
     </dataValidation>
-    <dataValidation sqref="BF2:BF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$T$2:$T$4</formula1>
+    <dataValidation sqref="BE2:BE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$T$2:$T$6</formula1>
     </dataValidation>
     <dataValidation sqref="BG2:BG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$U$2:$U$4</formula1>
     </dataValidation>
-    <dataValidation sqref="BJ2:BJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$V$2:$V$3</formula1>
+    <dataValidation sqref="BH2:BH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
-    <dataValidation sqref="BN2:BN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BK2:BK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$W$2:$W$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="BO2:BO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$X$2:$X$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3070,7 +3112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3086,105 +3128,110 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>sample_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tumor_descriptor</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>composition</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>file_source_platform</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>instrument_platform</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>end_bias</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>library_type</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>feature_type</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>probe_spike_in</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>UMI_barcode_read</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>cell_barcode_read</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>cDNA_read</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
@@ -3203,105 +3250,110 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Tumor</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Deceased</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Bone Marrow</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>bti_aws</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>FASTQ</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>MD5</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Complete Genomics</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>10x Flex GEX</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>3'-end</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>GEX</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Affinity Enrichment</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Stranded</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>gex</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3315,90 +3367,95 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Initial CNS Tumor</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Buffy Coat</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>local_drive</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>BAM</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>SHA1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Illumina</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>5'-end</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Hybrid Selection</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Unstranded</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3407,489 +3464,494 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
+          <t>Not Reported</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Virus-infected</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Metastatic</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Derived Cell Line</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>bti_aws_and_local_drive</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>BAI</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SHA256</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Ion Torrent</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Full-length</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>miRNA Size Fractionation</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>First Stranded</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Post-treatment</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>cgc</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>CRAM</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>SHA512</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>LS454</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>PCR</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Second Stranded</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Not Reported</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Primary Tumor</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Not Reported</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>kids_first</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>CRAI</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>ETag</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>SOLiD</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Poly-T Enrichment</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Progressive</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Patient Derived Xenograft</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>sra</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>GVCF</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>ONT</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Random</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Progressive Disease Post-Mortem</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Xenograft</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>synapse</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>VCF</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>DNBSEQ</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>rRNA Depletion</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Recurrence</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Patient Derived Organoid</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>TBI</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Relapse</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Peripheral Blood Mononuclear Cells</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>MAF</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Residual</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Peripheral Whole Blood</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Second Malignancy</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Saliva</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Solid Tissue</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>DCM</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Umbilical Cord Blood</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>IDAT</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Patient-Derived T Cells</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>SVS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Modified T Cells</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>GPR</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Patient-Derived Primary Cells</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>CNS</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>iPSC-Derived Organoid</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>TXT</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Cerebrospinal Fluid</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Embryonic Stem Cell Derived Cell Line</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>PED</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>SEG</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>TAR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>TSV</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>mzML</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>raw</t>
         </is>

--- a/excel_templates/single_cell_flex_manifest_template.xlsx
+++ b/excel_templates/single_cell_flex_manifest_template.xlsx
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version</t>
+          <t>Reference genome version. Required when file_format is "BAM" or "CRAM"</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
